--- a/CucumberDemoArchiture/testData/TestData2.xlsx
+++ b/CucumberDemoArchiture/testData/TestData2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="0" yWindow="2472" windowWidth="17952" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,11 +12,12 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Username</t>
   </si>
@@ -94,6 +95,27 @@
   </si>
   <si>
     <t>pass10</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>poor</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -439,14 +461,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,8 +478,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -467,8 +492,11 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -478,8 +506,11 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -489,8 +520,11 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -500,8 +534,11 @@
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -511,8 +548,11 @@
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -522,8 +562,11 @@
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -533,8 +576,11 @@
       <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -544,8 +590,11 @@
       <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -555,8 +604,11 @@
       <c r="C10" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -566,28 +618,31 @@
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
